--- a/strategy_packs/momentum_estrategia.xlsx
+++ b/strategy_packs/momentum_estrategia.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,6 +433,11 @@
           <t>filter_conditions</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publica</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -448,6 +453,11 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>{"op": "AND", "children": [{"cond": {"left": {"type": "indicator", "key": "trend_weekly"}, "operator": "in", "right": {"type": "const", "value": ["bullish", "bullish_strong", "bullish_nascent_strong"]}}}, {"cond": {"left": {"type": "indicator", "key": "dist_sma200"}, "operator": "&gt;", "right": {"type": "const", "value": 0}}}, {"cond": {"left": {"type": "indicator", "key": "volatility_daily"}, "operator": "not_in", "right": {"type": "const", "value": ["extrema_corta", "extrema_media", "extrema_larga"]}}}]}</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -511,9 +521,6 @@
       <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -529,9 +536,6 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -547,9 +551,6 @@
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -565,9 +566,6 @@
       <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/strategy_packs/momentum_estrategia.xlsx
+++ b/strategy_packs/momentum_estrategia.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,11 +545,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>alineacion_timeframes</t>
+          <t>dist_sma_d</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -560,11 +560,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dist_sma_d</t>
+          <t>tendencia_d</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Momentum de líderes</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>tendencia_w</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Momentum de líderes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tendencia_m</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_packs/momentum_estrategia.xlsx
+++ b/strategy_packs/momentum_estrategia.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,21 +491,6 @@
           <t>weight</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>group_type</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>group_id</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
